--- a/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_3_burden_coverage_calibration_source_data.xlsx
+++ b/Project 1 Data Quality Assessment/D4 Parallel-redundancy Temporal Consistency/outputs/figure_source_data/FigD4_3_burden_coverage_calibration_source_data.xlsx
@@ -480,10 +480,10 @@
         <v>45872</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02040816326530612</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -505,10 +505,10 @@
         <v>45879</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5535714285714286</v>
+        <v>0.375</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -530,19 +530,19 @@
         <v>45886</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.1118881118881119</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.6853146853146853</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="F4" t="n">
         <v>168</v>
       </c>
       <c r="G4" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5">
@@ -555,19 +555,19 @@
         <v>45893</v>
       </c>
       <c r="C5" t="n">
-        <v>0.311377245508982</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2994011976047904</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9940476190476191</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>168</v>
       </c>
       <c r="G5" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
@@ -580,10 +580,10 @@
         <v>45900</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.25</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -605,10 +605,10 @@
         <v>45907</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -630,19 +630,19 @@
         <v>45914</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8896551724137931</v>
+        <v>0.9712230215827338</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06206896551724138</v>
+        <v>0.01438848920863309</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8273809523809523</v>
       </c>
       <c r="F8" t="n">
         <v>168</v>
       </c>
       <c r="G8" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
@@ -655,10 +655,10 @@
         <v>45921</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3988095238095238</v>
+        <v>0.1845238095238095</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -680,10 +680,10 @@
         <v>45928</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.375</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -705,10 +705,10 @@
         <v>45935</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.25</v>
       </c>
       <c r="D11" t="n">
-        <v>0.125</v>
+        <v>0.3630952380952381</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -730,10 +730,10 @@
         <v>45942</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -755,10 +755,10 @@
         <v>45949</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>45956</v>
       </c>
       <c r="C14" t="n">
-        <v>0.244047619047619</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="D14" t="n">
-        <v>0.119047619047619</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -805,10 +805,10 @@
         <v>45963</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06547619047619048</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1011904761904762</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -830,10 +830,10 @@
         <v>45970</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1845238095238095</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -855,10 +855,10 @@
         <v>45977</v>
       </c>
       <c r="C17" t="n">
-        <v>0.25</v>
+        <v>0.244047619047619</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -880,10 +880,10 @@
         <v>45984</v>
       </c>
       <c r="C18" t="n">
-        <v>0.75</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -905,10 +905,10 @@
         <v>45991</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1607142857142857</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -930,10 +930,10 @@
         <v>45998</v>
       </c>
       <c r="C20" t="n">
-        <v>0.06547619047619048</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.125</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -980,10 +980,10 @@
         <v>46012</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="D22" t="n">
-        <v>0.005952380952380952</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -1005,10 +1005,10 @@
         <v>46019</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -1055,19 +1055,19 @@
         <v>46033</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4492753623188406</v>
+        <v>0.2148148148148148</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.3185185185185185</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="F25" t="n">
         <v>168</v>
       </c>
       <c r="G25" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
@@ -1080,10 +1080,10 @@
         <v>46040</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1105,10 +1105,10 @@
         <v>46047</v>
       </c>
       <c r="C27" t="n">
-        <v>0.005952380952380952</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.119047619047619</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1130,10 +1130,10 @@
         <v>46054</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -1155,10 +1155,10 @@
         <v>46061</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -1180,10 +1180,10 @@
         <v>46068</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3690476190476191</v>
+        <v>0.3869047619047619</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1205,10 +1205,10 @@
         <v>46075</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1011904761904762</v>
+        <v>0.0119047619047619</v>
       </c>
       <c r="D31" t="n">
-        <v>0.244047619047619</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1230,10 +1230,10 @@
         <v>46082</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5178571428571429</v>
+        <v>0.5595238095238095</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1255,10 +1255,10 @@
         <v>46089</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.4702380952380952</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.5119047619047619</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1280,10 +1280,10 @@
         <v>46096</v>
       </c>
       <c r="C34" t="n">
-        <v>0.130952380952381</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -1305,19 +1305,19 @@
         <v>46103</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1073825503355705</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1275167785234899</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8869047619047619</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>168</v>
       </c>
       <c r="G35" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36">
@@ -1330,10 +1330,10 @@
         <v>46110</v>
       </c>
       <c r="C36" t="n">
-        <v>0.625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1355,10 +1355,10 @@
         <v>46117</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5535714285714286</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1380,10 +1380,10 @@
         <v>46124</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -1405,19 +1405,19 @@
         <v>46131</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F39" t="n">
         <v>24</v>
       </c>
       <c r="G39" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -1430,10 +1430,10 @@
         <v>45872</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6326530612244898</v>
+        <v>0.3061224489795918</v>
       </c>
       <c r="D40" t="n">
-        <v>0.163265306122449</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -1455,10 +1455,10 @@
         <v>45879</v>
       </c>
       <c r="C41" t="n">
-        <v>0.5178571428571429</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.625</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
@@ -1480,19 +1480,19 @@
         <v>45886</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.05594405594405594</v>
       </c>
       <c r="D42" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="F42" t="n">
         <v>168</v>
       </c>
       <c r="G42" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43">
@@ -1505,7 +1505,7 @@
         <v>45893</v>
       </c>
       <c r="C43" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="D43" t="n">
         <v>0.8511904761904762</v>
@@ -1530,10 +1530,10 @@
         <v>45900</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="D44" t="n">
-        <v>0.7440476190476191</v>
+        <v>0.8630952380952381</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -1555,10 +1555,10 @@
         <v>45907</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="D45" t="n">
-        <v>0.6488095238095238</v>
+        <v>0.7738095238095238</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -1580,19 +1580,19 @@
         <v>45914</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5655172413793104</v>
+        <v>0.4100719424460432</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.4460431654676259</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8273809523809523</v>
       </c>
       <c r="F46" t="n">
         <v>168</v>
       </c>
       <c r="G46" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47">
@@ -1605,10 +1605,10 @@
         <v>45921</v>
       </c>
       <c r="C47" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.5595238095238095</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3690476190476191</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -1630,10 +1630,10 @@
         <v>45928</v>
       </c>
       <c r="C48" t="n">
-        <v>0.005952380952380952</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4345238095238095</v>
+        <v>0.6011904761904762</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -1655,10 +1655,10 @@
         <v>45935</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.5297619047619048</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -1680,10 +1680,10 @@
         <v>45942</v>
       </c>
       <c r="C50" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -1705,10 +1705,10 @@
         <v>45949</v>
       </c>
       <c r="C51" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="D51" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -1730,10 +1730,10 @@
         <v>45956</v>
       </c>
       <c r="C52" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D52" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -1755,10 +1755,10 @@
         <v>45963</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0119047619047619</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.05952380952380952</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>1</v>
@@ -1780,10 +1780,10 @@
         <v>45970</v>
       </c>
       <c r="C54" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="D54" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -1805,10 +1805,10 @@
         <v>45977</v>
       </c>
       <c r="C55" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -1830,10 +1830,10 @@
         <v>45984</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8154761904761905</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1011904761904762</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
@@ -1855,10 +1855,10 @@
         <v>45991</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="D57" t="n">
-        <v>0.3690476190476191</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E57" t="n">
         <v>1</v>
@@ -1883,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="E58" t="n">
         <v>1</v>
@@ -1905,10 +1905,10 @@
         <v>46005</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="D59" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -1930,10 +1930,10 @@
         <v>46012</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5297619047619048</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="E60" t="n">
         <v>1</v>
@@ -1955,7 +1955,7 @@
         <v>46019</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.7440476190476191</v>
       </c>
       <c r="D61" t="n">
         <v>0.130952380952381</v>
@@ -1980,10 +1980,10 @@
         <v>46026</v>
       </c>
       <c r="C62" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D62" t="n">
         <v>0.4345238095238095</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.3869047619047619</v>
       </c>
       <c r="E62" t="n">
         <v>1</v>
@@ -2005,19 +2005,19 @@
         <v>46033</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.5407407407407407</v>
       </c>
       <c r="D63" t="n">
-        <v>0.1884057971014493</v>
+        <v>0.2740740740740741</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="F63" t="n">
         <v>168</v>
       </c>
       <c r="G63" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="64">
@@ -2030,7 +2030,7 @@
         <v>46040</v>
       </c>
       <c r="C64" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="D64" t="n">
         <v>0.3095238095238095</v>
@@ -2055,10 +2055,10 @@
         <v>46047</v>
       </c>
       <c r="C65" t="n">
-        <v>0.119047619047619</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="D65" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E65" t="n">
         <v>1</v>
@@ -2080,10 +2080,10 @@
         <v>46054</v>
       </c>
       <c r="C66" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="D66" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2105,10 +2105,10 @@
         <v>46061</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="E67" t="n">
         <v>1</v>
@@ -2130,10 +2130,10 @@
         <v>46068</v>
       </c>
       <c r="C68" t="n">
-        <v>0.1011904761904762</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="D68" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -2155,10 +2155,10 @@
         <v>46075</v>
       </c>
       <c r="C69" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="D69" t="n">
-        <v>0.130952380952381</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -2180,10 +2180,10 @@
         <v>46082</v>
       </c>
       <c r="C70" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="D70" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -2205,10 +2205,10 @@
         <v>46089</v>
       </c>
       <c r="C71" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.1011904761904762</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.4345238095238095</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -2255,19 +2255,19 @@
         <v>46103</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1140939597315436</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4161073825503356</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8869047619047619</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>168</v>
       </c>
       <c r="G73" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74">
@@ -2280,10 +2280,10 @@
         <v>46110</v>
       </c>
       <c r="C74" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="D74" t="n">
         <v>0.1071428571428571</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0.1785714285714286</v>
       </c>
       <c r="E74" t="n">
         <v>1</v>
@@ -2305,7 +2305,7 @@
         <v>46117</v>
       </c>
       <c r="C75" t="n">
-        <v>0.03571428571428571</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0.3630952380952381</v>
@@ -2330,10 +2330,10 @@
         <v>46124</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="D76" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.375</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
@@ -2355,19 +2355,19 @@
         <v>46131</v>
       </c>
       <c r="C77" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F77" t="n">
         <v>24</v>
       </c>
       <c r="G77" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78">
@@ -2405,10 +2405,10 @@
         <v>45879</v>
       </c>
       <c r="C79" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.2321428571428572</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
@@ -2430,19 +2430,19 @@
         <v>45886</v>
       </c>
       <c r="C80" t="n">
-        <v>0.125</v>
+        <v>0.04195804195804196</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.1888111888111888</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="F80" t="n">
         <v>168</v>
       </c>
       <c r="G80" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="81">
@@ -2455,10 +2455,10 @@
         <v>45893</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.1130952380952381</v>
       </c>
       <c r="D81" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.7440476190476191</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2480,10 +2480,10 @@
         <v>45900</v>
       </c>
       <c r="C82" t="n">
-        <v>0.3214285714285715</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="D82" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.7976190476190477</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -2505,10 +2505,10 @@
         <v>45907</v>
       </c>
       <c r="C83" t="n">
-        <v>0.4226190476190476</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="D83" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.7559523809523809</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
@@ -2530,19 +2530,19 @@
         <v>45914</v>
       </c>
       <c r="C84" t="n">
-        <v>0.3862068965517241</v>
+        <v>0.2949640287769784</v>
       </c>
       <c r="D84" t="n">
-        <v>0.1517241379310345</v>
+        <v>0.09352517985611511</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8273809523809523</v>
       </c>
       <c r="F84" t="n">
         <v>168</v>
       </c>
       <c r="G84" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="85">
@@ -2555,10 +2555,10 @@
         <v>45921</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.4345238095238095</v>
       </c>
       <c r="D85" t="n">
-        <v>0.1011904761904762</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -2580,10 +2580,10 @@
         <v>45928</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="D86" t="n">
-        <v>0.02380952380952381</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -2605,10 +2605,10 @@
         <v>45935</v>
       </c>
       <c r="C87" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.125</v>
       </c>
       <c r="D87" t="n">
-        <v>0.06547619047619048</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -2630,10 +2630,10 @@
         <v>45942</v>
       </c>
       <c r="C88" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="D88" t="n">
-        <v>0.119047619047619</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -2655,10 +2655,10 @@
         <v>45949</v>
       </c>
       <c r="C89" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.375</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -2680,10 +2680,10 @@
         <v>45956</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.25</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="E90" t="n">
         <v>1</v>
@@ -2705,10 +2705,10 @@
         <v>45963</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1130952380952381</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
@@ -2730,10 +2730,10 @@
         <v>45970</v>
       </c>
       <c r="C92" t="n">
-        <v>0.3511904761904762</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.2559523809523809</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -2755,10 +2755,10 @@
         <v>45977</v>
       </c>
       <c r="C93" t="n">
-        <v>0.3154761904761905</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E93" t="n">
         <v>1</v>
@@ -2780,10 +2780,10 @@
         <v>45984</v>
       </c>
       <c r="C94" t="n">
-        <v>0.3988095238095238</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4107142857142857</v>
+        <v>0.4226190476190476</v>
       </c>
       <c r="E94" t="n">
         <v>1</v>
@@ -2805,10 +2805,10 @@
         <v>45991</v>
       </c>
       <c r="C95" t="n">
-        <v>0.375</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.625</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -2830,10 +2830,10 @@
         <v>45998</v>
       </c>
       <c r="C96" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D96" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.5773809523809523</v>
       </c>
       <c r="E96" t="n">
         <v>1</v>
@@ -2855,10 +2855,10 @@
         <v>46005</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3154761904761905</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6726190476190477</v>
       </c>
       <c r="E97" t="n">
         <v>1</v>
@@ -2880,10 +2880,10 @@
         <v>46012</v>
       </c>
       <c r="C98" t="n">
-        <v>0.3511904761904762</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="D98" t="n">
-        <v>0.1845238095238095</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E98" t="n">
         <v>1</v>
@@ -2905,10 +2905,10 @@
         <v>46019</v>
       </c>
       <c r="C99" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.4404761904761905</v>
       </c>
       <c r="D99" t="n">
-        <v>0.3273809523809524</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="E99" t="n">
         <v>1</v>
@@ -2930,10 +2930,10 @@
         <v>46026</v>
       </c>
       <c r="C100" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E100" t="n">
         <v>1</v>
@@ -2955,19 +2955,19 @@
         <v>46033</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2536231884057971</v>
+        <v>0.007407407407407408</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3405797101449275</v>
+        <v>0.3185185185185185</v>
       </c>
       <c r="E101" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="F101" t="n">
         <v>168</v>
       </c>
       <c r="G101" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="102">
@@ -2980,10 +2980,10 @@
         <v>46040</v>
       </c>
       <c r="C102" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="D102" t="n">
-        <v>0.244047619047619</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -3005,10 +3005,10 @@
         <v>46047</v>
       </c>
       <c r="C103" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="E103" t="n">
         <v>1</v>
@@ -3030,10 +3030,10 @@
         <v>46054</v>
       </c>
       <c r="C104" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="D104" t="n">
-        <v>0.375</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="E104" t="n">
         <v>1</v>
@@ -3055,10 +3055,10 @@
         <v>46061</v>
       </c>
       <c r="C105" t="n">
-        <v>0.5297619047619048</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
@@ -3080,10 +3080,10 @@
         <v>46068</v>
       </c>
       <c r="C106" t="n">
-        <v>0.6607142857142857</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="D106" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.3273809523809524</v>
       </c>
       <c r="E106" t="n">
         <v>1</v>
@@ -3105,10 +3105,10 @@
         <v>46075</v>
       </c>
       <c r="C107" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E107" t="n">
         <v>1</v>
@@ -3130,10 +3130,10 @@
         <v>46082</v>
       </c>
       <c r="C108" t="n">
-        <v>0.5535714285714286</v>
+        <v>0.5</v>
       </c>
       <c r="D108" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E108" t="n">
         <v>1</v>
@@ -3155,10 +3155,10 @@
         <v>46089</v>
       </c>
       <c r="C109" t="n">
-        <v>0.6130952380952381</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.244047619047619</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -3180,10 +3180,10 @@
         <v>46096</v>
       </c>
       <c r="C110" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D110" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="E110" t="n">
         <v>1</v>
@@ -3205,19 +3205,19 @@
         <v>46103</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5973154362416108</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="D111" t="n">
-        <v>0.261744966442953</v>
+        <v>0.3630952380952381</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8869047619047619</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
         <v>168</v>
       </c>
       <c r="G111" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="112">
@@ -3230,10 +3230,10 @@
         <v>46110</v>
       </c>
       <c r="C112" t="n">
-        <v>0.6369047619047619</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -3255,10 +3255,10 @@
         <v>46117</v>
       </c>
       <c r="C113" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -3280,10 +3280,10 @@
         <v>46124</v>
       </c>
       <c r="C114" t="n">
-        <v>0.6011904761904762</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3311,13 +3311,13 @@
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F115" t="n">
         <v>24</v>
       </c>
       <c r="G115" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116">
@@ -3330,10 +3330,10 @@
         <v>45872</v>
       </c>
       <c r="C116" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.163265306122449</v>
       </c>
       <c r="D116" t="n">
-        <v>0.2244897959183673</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3355,10 +3355,10 @@
         <v>45879</v>
       </c>
       <c r="C117" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="D117" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="E117" t="n">
         <v>1</v>
@@ -3380,19 +3380,19 @@
         <v>45886</v>
       </c>
       <c r="C118" t="n">
-        <v>0.5595238095238095</v>
+        <v>0.2867132867132867</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.4335664335664335</v>
       </c>
       <c r="E118" t="n">
-        <v>1</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="F118" t="n">
         <v>168</v>
       </c>
       <c r="G118" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="119">
@@ -3405,10 +3405,10 @@
         <v>45893</v>
       </c>
       <c r="C119" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="D119" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -3430,10 +3430,10 @@
         <v>45900</v>
       </c>
       <c r="C120" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8154761904761905</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1845238095238095</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -3455,10 +3455,10 @@
         <v>45907</v>
       </c>
       <c r="C121" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.3035714285714285</v>
       </c>
       <c r="D121" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.25</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -3480,19 +3480,19 @@
         <v>45914</v>
       </c>
       <c r="C122" t="n">
-        <v>0.896551724137931</v>
+        <v>0.7769784172661871</v>
       </c>
       <c r="D122" t="n">
-        <v>0.01379310344827586</v>
+        <v>0.1151079136690648</v>
       </c>
       <c r="E122" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8273809523809523</v>
       </c>
       <c r="F122" t="n">
         <v>168</v>
       </c>
       <c r="G122" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="123">
@@ -3530,10 +3530,10 @@
         <v>45928</v>
       </c>
       <c r="C124" t="n">
-        <v>0.875</v>
+        <v>0.9702380952380952</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1011904761904762</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="E124" t="n">
         <v>1</v>
@@ -3555,10 +3555,10 @@
         <v>45935</v>
       </c>
       <c r="C125" t="n">
-        <v>0.8511904761904762</v>
+        <v>0.8809523809523809</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="E125" t="n">
         <v>1</v>
@@ -3580,10 +3580,10 @@
         <v>45942</v>
       </c>
       <c r="C126" t="n">
-        <v>0.9940476190476191</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>0.005952380952380952</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
         <v>1</v>
@@ -3605,10 +3605,10 @@
         <v>45949</v>
       </c>
       <c r="C127" t="n">
-        <v>0.3988095238095238</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="E127" t="n">
         <v>1</v>
@@ -3630,10 +3630,10 @@
         <v>45956</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D128" t="n">
-        <v>0.1011904761904762</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
@@ -3655,10 +3655,10 @@
         <v>45963</v>
       </c>
       <c r="C129" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="D129" t="n">
-        <v>0.1130952380952381</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
@@ -3680,10 +3680,10 @@
         <v>45970</v>
       </c>
       <c r="C130" t="n">
-        <v>0.625</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="D130" t="n">
-        <v>0.125</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -3705,7 +3705,7 @@
         <v>45977</v>
       </c>
       <c r="C131" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="D131" t="n">
         <v>0.2738095238095238</v>
@@ -3730,10 +3730,10 @@
         <v>45984</v>
       </c>
       <c r="C132" t="n">
-        <v>0.4940476190476191</v>
+        <v>0.3630952380952381</v>
       </c>
       <c r="D132" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -3758,7 +3758,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="E133" t="n">
         <v>1</v>
@@ -3780,10 +3780,10 @@
         <v>45998</v>
       </c>
       <c r="C134" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="D134" t="n">
-        <v>0.5297619047619048</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E134" t="n">
         <v>1</v>
@@ -3805,10 +3805,10 @@
         <v>46005</v>
       </c>
       <c r="C135" t="n">
-        <v>0.5059523809523809</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="D135" t="n">
-        <v>0.3869047619047619</v>
+        <v>0.4464285714285715</v>
       </c>
       <c r="E135" t="n">
         <v>1</v>
@@ -3833,7 +3833,7 @@
         <v>0.2142857142857143</v>
       </c>
       <c r="D136" t="n">
-        <v>0.4404761904761905</v>
+        <v>0.3869047619047619</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -3855,10 +3855,10 @@
         <v>46019</v>
       </c>
       <c r="C137" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.5</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="E137" t="n">
         <v>1</v>
@@ -3880,7 +3880,7 @@
         <v>46026</v>
       </c>
       <c r="C138" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.5654761904761905</v>
       </c>
       <c r="D138" t="n">
         <v>0.2738095238095238</v>
@@ -3905,19 +3905,19 @@
         <v>46033</v>
       </c>
       <c r="C139" t="n">
-        <v>0.5579710144927537</v>
+        <v>0.4370370370370371</v>
       </c>
       <c r="D139" t="n">
-        <v>0.108695652173913</v>
+        <v>0.1703703703703704</v>
       </c>
       <c r="E139" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="F139" t="n">
         <v>168</v>
       </c>
       <c r="G139" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="140">
@@ -3930,10 +3930,10 @@
         <v>46040</v>
       </c>
       <c r="C140" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="D140" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="E140" t="n">
         <v>1</v>
@@ -3958,7 +3958,7 @@
         <v>0.02976190476190476</v>
       </c>
       <c r="D141" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.07142857142857142</v>
+        <v>0</v>
       </c>
       <c r="E142" t="n">
         <v>1</v>
@@ -4005,10 +4005,10 @@
         <v>46061</v>
       </c>
       <c r="C143" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="D143" t="n">
         <v>0.119047619047619</v>
-      </c>
-      <c r="D143" t="n">
-        <v>0.3035714285714285</v>
       </c>
       <c r="E143" t="n">
         <v>1</v>
@@ -4030,7 +4030,7 @@
         <v>46068</v>
       </c>
       <c r="C144" t="n">
-        <v>0.2738095238095238</v>
+        <v>0.244047619047619</v>
       </c>
       <c r="D144" t="n">
         <v>0.7261904761904762</v>
@@ -4055,10 +4055,10 @@
         <v>46075</v>
       </c>
       <c r="C145" t="n">
-        <v>0.09523809523809523</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.7261904761904762</v>
+        <v>0.7976190476190477</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
@@ -4105,10 +4105,10 @@
         <v>46089</v>
       </c>
       <c r="C147" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5</v>
+        <v>0.4702380952380952</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4130,10 +4130,10 @@
         <v>46096</v>
       </c>
       <c r="C148" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="E148" t="n">
         <v>1</v>
@@ -4155,19 +4155,19 @@
         <v>46103</v>
       </c>
       <c r="C149" t="n">
-        <v>0.3154362416107382</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="D149" t="n">
-        <v>0.4161073825503356</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="E149" t="n">
-        <v>0.8869047619047619</v>
+        <v>1</v>
       </c>
       <c r="F149" t="n">
         <v>168</v>
       </c>
       <c r="G149" t="n">
-        <v>149</v>
+        <v>168</v>
       </c>
     </row>
     <row r="150">
@@ -4183,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E150" t="n">
         <v>1</v>
@@ -4208,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0.7738095238095238</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="E151" t="n">
         <v>1</v>
@@ -4230,10 +4230,10 @@
         <v>46124</v>
       </c>
       <c r="C152" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="D152" t="n">
-        <v>0.3630952380952381</v>
+        <v>0.6845238095238095</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4255,19 +4255,19 @@
         <v>46131</v>
       </c>
       <c r="C153" t="n">
-        <v>0.6</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="D153" t="n">
-        <v>0.4</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="E153" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F153" t="n">
         <v>24</v>
       </c>
       <c r="G153" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154">
@@ -4280,10 +4280,10 @@
         <v>45872</v>
       </c>
       <c r="C154" t="n">
-        <v>0.04081632653061224</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0.6530612244897959</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
@@ -4305,10 +4305,10 @@
         <v>45879</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4226190476190476</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="D155" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4330,19 +4330,19 @@
         <v>45886</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.2097902097902098</v>
       </c>
       <c r="D156" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.3006993006993007</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="F156" t="n">
         <v>168</v>
       </c>
       <c r="G156" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="157">
@@ -4355,10 +4355,10 @@
         <v>45893</v>
       </c>
       <c r="C157" t="n">
-        <v>0.06547619047619048</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D157" t="n">
-        <v>0.6369047619047619</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -4405,10 +4405,10 @@
         <v>45907</v>
       </c>
       <c r="C159" t="n">
-        <v>0.04166666666666666</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.25</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -4430,19 +4430,19 @@
         <v>45914</v>
       </c>
       <c r="C160" t="n">
-        <v>0.3724137931034483</v>
+        <v>0.2949640287769784</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1379310344827586</v>
+        <v>0.04316546762589928</v>
       </c>
       <c r="E160" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8273809523809523</v>
       </c>
       <c r="F160" t="n">
         <v>168</v>
       </c>
       <c r="G160" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="161">
@@ -4455,10 +4455,10 @@
         <v>45921</v>
       </c>
       <c r="C161" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="E161" t="n">
         <v>1</v>
@@ -4480,10 +4480,10 @@
         <v>45928</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D162" t="n">
-        <v>0.25</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
@@ -4505,10 +4505,10 @@
         <v>45935</v>
       </c>
       <c r="C163" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="D163" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="E163" t="n">
         <v>1</v>
@@ -4530,10 +4530,10 @@
         <v>45942</v>
       </c>
       <c r="C164" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="E164" t="n">
         <v>1</v>
@@ -4555,10 +4555,10 @@
         <v>45949</v>
       </c>
       <c r="C165" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="D165" t="n">
-        <v>0.4226190476190476</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="E165" t="n">
         <v>1</v>
@@ -4580,10 +4580,10 @@
         <v>45956</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="D166" t="n">
-        <v>0.1607142857142857</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E166" t="n">
         <v>1</v>
@@ -4605,10 +4605,10 @@
         <v>45963</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0119047619047619</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>0.07738095238095238</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
@@ -4630,10 +4630,10 @@
         <v>45970</v>
       </c>
       <c r="C168" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.2559523809523809</v>
       </c>
       <c r="D168" t="n">
-        <v>0.1130952380952381</v>
+        <v>0.3035714285714285</v>
       </c>
       <c r="E168" t="n">
         <v>1</v>
@@ -4655,10 +4655,10 @@
         <v>45977</v>
       </c>
       <c r="C169" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="D169" t="n">
         <v>0.3392857142857143</v>
-      </c>
-      <c r="D169" t="n">
-        <v>0.375</v>
       </c>
       <c r="E169" t="n">
         <v>1</v>
@@ -4680,10 +4680,10 @@
         <v>45984</v>
       </c>
       <c r="C170" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.0119047619047619</v>
       </c>
       <c r="D170" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="E170" t="n">
         <v>1</v>
@@ -4730,10 +4730,10 @@
         <v>45998</v>
       </c>
       <c r="C172" t="n">
-        <v>0.01785714285714286</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>0.07738095238095238</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
@@ -4755,10 +4755,10 @@
         <v>46005</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="D173" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E173" t="n">
         <v>1</v>
@@ -4780,10 +4780,10 @@
         <v>46012</v>
       </c>
       <c r="C174" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="D174" t="n">
-        <v>0.02976190476190476</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="E174" t="n">
         <v>1</v>
@@ -4805,10 +4805,10 @@
         <v>46019</v>
       </c>
       <c r="C175" t="n">
-        <v>0.3511904761904762</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="D175" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.375</v>
       </c>
       <c r="E175" t="n">
         <v>1</v>
@@ -4830,10 +4830,10 @@
         <v>46026</v>
       </c>
       <c r="C176" t="n">
-        <v>0.244047619047619</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="D176" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -4855,19 +4855,19 @@
         <v>46033</v>
       </c>
       <c r="C177" t="n">
-        <v>0.02173913043478261</v>
+        <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>0.2753623188405797</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="E177" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="F177" t="n">
         <v>168</v>
       </c>
       <c r="G177" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="178">
@@ -4880,10 +4880,10 @@
         <v>46040</v>
       </c>
       <c r="C178" t="n">
-        <v>0.005952380952380952</v>
+        <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>0.07142857142857142</v>
+        <v>0</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -4905,10 +4905,10 @@
         <v>46047</v>
       </c>
       <c r="C179" t="n">
-        <v>0.02976190476190476</v>
+        <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
         <v>1</v>
@@ -4930,10 +4930,10 @@
         <v>46054</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="D180" t="n">
-        <v>0.3154761904761905</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="E180" t="n">
         <v>1</v>
@@ -4955,10 +4955,10 @@
         <v>46061</v>
       </c>
       <c r="C181" t="n">
-        <v>0.2678571428571428</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="D181" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="E181" t="n">
         <v>1</v>
@@ -4980,10 +4980,10 @@
         <v>46068</v>
       </c>
       <c r="C182" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="D182" t="n">
-        <v>0.3392857142857143</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="E182" t="n">
         <v>1</v>
@@ -5005,10 +5005,10 @@
         <v>46075</v>
       </c>
       <c r="C183" t="n">
-        <v>0.3511904761904762</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="D183" t="n">
-        <v>0.1785714285714286</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="E183" t="n">
         <v>1</v>
@@ -5030,10 +5030,10 @@
         <v>46082</v>
       </c>
       <c r="C184" t="n">
-        <v>0.01785714285714286</v>
+        <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="E184" t="n">
         <v>1</v>
@@ -5055,10 +5055,10 @@
         <v>46089</v>
       </c>
       <c r="C185" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.05357142857142857</v>
       </c>
       <c r="D185" t="n">
-        <v>0.3571428571428572</v>
+        <v>0.125</v>
       </c>
       <c r="E185" t="n">
         <v>1</v>
@@ -5080,10 +5080,10 @@
         <v>46096</v>
       </c>
       <c r="C186" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="D186" t="n">
-        <v>0.2321428571428572</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E186" t="n">
         <v>1</v>
@@ -5105,10 +5105,10 @@
         <v>46103</v>
       </c>
       <c r="C187" t="n">
-        <v>0.5654761904761905</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="D187" t="n">
-        <v>0.125</v>
+        <v>0.25</v>
       </c>
       <c r="E187" t="n">
         <v>1</v>
@@ -5130,10 +5130,10 @@
         <v>46110</v>
       </c>
       <c r="C188" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="D188" t="n">
-        <v>0.05952380952380952</v>
+        <v>0.5535714285714286</v>
       </c>
       <c r="E188" t="n">
         <v>1</v>
@@ -5155,10 +5155,10 @@
         <v>46117</v>
       </c>
       <c r="C189" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="D189" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E189" t="n">
         <v>1</v>
@@ -5180,10 +5180,10 @@
         <v>46124</v>
       </c>
       <c r="C190" t="n">
-        <v>0.25</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="D190" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="E190" t="n">
         <v>1</v>
@@ -5211,13 +5211,13 @@
         <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F191" t="n">
         <v>24</v>
       </c>
       <c r="G191" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192">
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>0.04081632653061224</v>
+        <v>0</v>
       </c>
       <c r="E192" t="n">
         <v>1</v>
@@ -5255,10 +5255,10 @@
         <v>45879</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="D193" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.125</v>
       </c>
       <c r="E193" t="n">
         <v>1</v>
@@ -5280,19 +5280,19 @@
         <v>45886</v>
       </c>
       <c r="C194" t="n">
-        <v>0.3690476190476191</v>
+        <v>0.04195804195804196</v>
       </c>
       <c r="D194" t="n">
-        <v>0.5</v>
+        <v>0.4965034965034965</v>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="F194" t="n">
         <v>168</v>
       </c>
       <c r="G194" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="195">
@@ -5305,10 +5305,10 @@
         <v>45893</v>
       </c>
       <c r="C195" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="D195" t="n">
-        <v>0.130952380952381</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="E195" t="n">
         <v>1</v>
@@ -5330,10 +5330,10 @@
         <v>45900</v>
       </c>
       <c r="C196" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D196" t="n">
-        <v>0.3690476190476191</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="E196" t="n">
         <v>1</v>
@@ -5355,10 +5355,10 @@
         <v>45907</v>
       </c>
       <c r="C197" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.0119047619047619</v>
       </c>
       <c r="D197" t="n">
-        <v>0.375</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="E197" t="n">
         <v>1</v>
@@ -5380,19 +5380,19 @@
         <v>45914</v>
       </c>
       <c r="C198" t="n">
-        <v>0.08275862068965517</v>
+        <v>0.007194244604316547</v>
       </c>
       <c r="D198" t="n">
-        <v>0.103448275862069</v>
+        <v>0.04316546762589928</v>
       </c>
       <c r="E198" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8273809523809523</v>
       </c>
       <c r="F198" t="n">
         <v>168</v>
       </c>
       <c r="G198" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="199">
@@ -5405,10 +5405,10 @@
         <v>45921</v>
       </c>
       <c r="C199" t="n">
-        <v>0.6726190476190477</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="D199" t="n">
-        <v>0.130952380952381</v>
+        <v>0.3630952380952381</v>
       </c>
       <c r="E199" t="n">
         <v>1</v>
@@ -5430,10 +5430,10 @@
         <v>45928</v>
       </c>
       <c r="C200" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="D200" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="E200" t="n">
         <v>1</v>
@@ -5455,7 +5455,7 @@
         <v>45935</v>
       </c>
       <c r="C201" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="D201" t="n">
         <v>0.1130952380952381</v>
@@ -5480,10 +5480,10 @@
         <v>45942</v>
       </c>
       <c r="C202" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="D202" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E202" t="n">
         <v>1</v>
@@ -5505,10 +5505,10 @@
         <v>45949</v>
       </c>
       <c r="C203" t="n">
-        <v>0.3452380952380952</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="D203" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.2321428571428572</v>
       </c>
       <c r="E203" t="n">
         <v>1</v>
@@ -5530,10 +5530,10 @@
         <v>45956</v>
       </c>
       <c r="C204" t="n">
-        <v>0.1964285714285714</v>
+        <v>0.1369047619047619</v>
       </c>
       <c r="D204" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="E204" t="n">
         <v>1</v>
@@ -5555,10 +5555,10 @@
         <v>45963</v>
       </c>
       <c r="C205" t="n">
-        <v>0.6845238095238095</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="D205" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="E205" t="n">
         <v>1</v>
@@ -5580,10 +5580,10 @@
         <v>45970</v>
       </c>
       <c r="C206" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="D206" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="E206" t="n">
         <v>1</v>
@@ -5605,10 +5605,10 @@
         <v>45977</v>
       </c>
       <c r="C207" t="n">
-        <v>0.1845238095238095</v>
+        <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0.2023809523809524</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="E207" t="n">
         <v>1</v>
@@ -5630,10 +5630,10 @@
         <v>45984</v>
       </c>
       <c r="C208" t="n">
-        <v>0.2797619047619048</v>
+        <v>0.06547619047619048</v>
       </c>
       <c r="D208" t="n">
-        <v>0.244047619047619</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="E208" t="n">
         <v>1</v>
@@ -5655,10 +5655,10 @@
         <v>45991</v>
       </c>
       <c r="C209" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="D209" t="n">
-        <v>0.25</v>
+        <v>0.1488095238095238</v>
       </c>
       <c r="E209" t="n">
         <v>1</v>
@@ -5680,10 +5680,10 @@
         <v>45998</v>
       </c>
       <c r="C210" t="n">
-        <v>0.1369047619047619</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="D210" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.02976190476190476</v>
       </c>
       <c r="E210" t="n">
         <v>1</v>
@@ -5705,10 +5705,10 @@
         <v>46005</v>
       </c>
       <c r="C211" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="D211" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.1011904761904762</v>
       </c>
       <c r="E211" t="n">
         <v>1</v>
@@ -5730,10 +5730,10 @@
         <v>46012</v>
       </c>
       <c r="C212" t="n">
-        <v>0.4345238095238095</v>
+        <v>0.1845238095238095</v>
       </c>
       <c r="D212" t="n">
-        <v>0.2619047619047619</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="E212" t="n">
         <v>1</v>
@@ -5755,10 +5755,10 @@
         <v>46019</v>
       </c>
       <c r="C213" t="n">
-        <v>0.9880952380952381</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="D213" t="n">
-        <v>0.0119047619047619</v>
+        <v>0.2797619047619048</v>
       </c>
       <c r="E213" t="n">
         <v>1</v>
@@ -5780,10 +5780,10 @@
         <v>46026</v>
       </c>
       <c r="C214" t="n">
-        <v>1</v>
+        <v>0.7559523809523809</v>
       </c>
       <c r="D214" t="n">
-        <v>0</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="E214" t="n">
         <v>1</v>
@@ -5805,19 +5805,19 @@
         <v>46033</v>
       </c>
       <c r="C215" t="n">
-        <v>0.8623188405797102</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="D215" t="n">
-        <v>0.05797101449275362</v>
+        <v>0.3111111111111111</v>
       </c>
       <c r="E215" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="F215" t="n">
         <v>168</v>
       </c>
       <c r="G215" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="216">
@@ -5830,10 +5830,10 @@
         <v>46040</v>
       </c>
       <c r="C216" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.07738095238095238</v>
       </c>
       <c r="D216" t="n">
-        <v>0.3154761904761905</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E216" t="n">
         <v>1</v>
@@ -5855,10 +5855,10 @@
         <v>46047</v>
       </c>
       <c r="C217" t="n">
-        <v>0.1488095238095238</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.08928571428571429</v>
       </c>
       <c r="E217" t="n">
         <v>1</v>
@@ -5880,10 +5880,10 @@
         <v>46054</v>
       </c>
       <c r="C218" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.5773809523809523</v>
       </c>
       <c r="D218" t="n">
-        <v>0.09523809523809523</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="E218" t="n">
         <v>1</v>
@@ -5905,10 +5905,10 @@
         <v>46061</v>
       </c>
       <c r="C219" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.2559523809523809</v>
       </c>
       <c r="D219" t="n">
-        <v>0.1488095238095238</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E219" t="n">
         <v>1</v>
@@ -5930,10 +5930,10 @@
         <v>46068</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>0.6726190476190477</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E220" t="n">
         <v>1</v>
@@ -5955,10 +5955,10 @@
         <v>46075</v>
       </c>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>0.7559523809523809</v>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="E221" t="n">
         <v>1</v>
@@ -5980,10 +5980,10 @@
         <v>46082</v>
       </c>
       <c r="C222" t="n">
-        <v>1</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="E222" t="n">
         <v>1</v>
@@ -6005,10 +6005,10 @@
         <v>46089</v>
       </c>
       <c r="C223" t="n">
-        <v>0.9404761904761905</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D223" t="n">
-        <v>0.01785714285714286</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="E223" t="n">
         <v>1</v>
@@ -6030,10 +6030,10 @@
         <v>46096</v>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="D224" t="n">
-        <v>0</v>
+        <v>0.1845238095238095</v>
       </c>
       <c r="E224" t="n">
         <v>1</v>
@@ -6055,10 +6055,10 @@
         <v>46103</v>
       </c>
       <c r="C225" t="n">
-        <v>1</v>
+        <v>0.5654761904761905</v>
       </c>
       <c r="D225" t="n">
-        <v>0</v>
+        <v>0.3392857142857143</v>
       </c>
       <c r="E225" t="n">
         <v>1</v>
@@ -6080,10 +6080,10 @@
         <v>46110</v>
       </c>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>0.5892857142857143</v>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E226" t="n">
         <v>1</v>
@@ -6105,10 +6105,10 @@
         <v>46117</v>
       </c>
       <c r="C227" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.3690476190476191</v>
       </c>
       <c r="D227" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="E227" t="n">
         <v>1</v>
@@ -6130,10 +6130,10 @@
         <v>46124</v>
       </c>
       <c r="C228" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="D228" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="E228" t="n">
         <v>1</v>
@@ -6155,19 +6155,19 @@
         <v>46131</v>
       </c>
       <c r="C229" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F229" t="n">
         <v>24</v>
       </c>
       <c r="G229" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230">
@@ -6180,10 +6180,10 @@
         <v>45872</v>
       </c>
       <c r="C230" t="n">
-        <v>0.5918367346938775</v>
+        <v>0.5510204081632653</v>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="E230" t="n">
         <v>1</v>
@@ -6205,10 +6205,10 @@
         <v>45879</v>
       </c>
       <c r="C231" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.6369047619047619</v>
       </c>
       <c r="D231" t="n">
-        <v>0.119047619047619</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="E231" t="n">
         <v>1</v>
@@ -6230,19 +6230,19 @@
         <v>45886</v>
       </c>
       <c r="C232" t="n">
-        <v>0.7738095238095238</v>
+        <v>0.4895104895104895</v>
       </c>
       <c r="D232" t="n">
-        <v>0.125</v>
+        <v>0.2587412587412588</v>
       </c>
       <c r="E232" t="n">
-        <v>1</v>
+        <v>0.8511904761904762</v>
       </c>
       <c r="F232" t="n">
         <v>168</v>
       </c>
       <c r="G232" t="n">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="233">
@@ -6255,10 +6255,10 @@
         <v>45893</v>
       </c>
       <c r="C233" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="D233" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.375</v>
       </c>
       <c r="E233" t="n">
         <v>1</v>
@@ -6280,10 +6280,10 @@
         <v>45900</v>
       </c>
       <c r="C234" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="D234" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="E234" t="n">
         <v>1</v>
@@ -6305,10 +6305,10 @@
         <v>45907</v>
       </c>
       <c r="C235" t="n">
-        <v>0.6369047619047619</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="D235" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E235" t="n">
         <v>1</v>
@@ -6330,19 +6330,19 @@
         <v>45914</v>
       </c>
       <c r="C236" t="n">
-        <v>0.7517241379310344</v>
+        <v>0.5611510791366906</v>
       </c>
       <c r="D236" t="n">
-        <v>0.06896551724137931</v>
+        <v>0.1223021582733813</v>
       </c>
       <c r="E236" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8273809523809523</v>
       </c>
       <c r="F236" t="n">
         <v>168</v>
       </c>
       <c r="G236" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="237">
@@ -6355,10 +6355,10 @@
         <v>45921</v>
       </c>
       <c r="C237" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="D237" t="n">
-        <v>0.1130952380952381</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="E237" t="n">
         <v>1</v>
@@ -6380,10 +6380,10 @@
         <v>45928</v>
       </c>
       <c r="C238" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D238" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="E238" t="n">
         <v>1</v>
@@ -6405,10 +6405,10 @@
         <v>45935</v>
       </c>
       <c r="C239" t="n">
-        <v>0.4940476190476191</v>
+        <v>0.1785714285714286</v>
       </c>
       <c r="D239" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E239" t="n">
         <v>1</v>
@@ -6430,10 +6430,10 @@
         <v>45942</v>
       </c>
       <c r="C240" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="D240" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.1845238095238095</v>
       </c>
       <c r="E240" t="n">
         <v>1</v>
@@ -6455,10 +6455,10 @@
         <v>45949</v>
       </c>
       <c r="C241" t="n">
-        <v>0.7678571428571429</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="D241" t="n">
-        <v>0.130952380952381</v>
+        <v>0.2202380952380952</v>
       </c>
       <c r="E241" t="n">
         <v>1</v>
@@ -6480,10 +6480,10 @@
         <v>45956</v>
       </c>
       <c r="C242" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.25</v>
       </c>
       <c r="D242" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.130952380952381</v>
       </c>
       <c r="E242" t="n">
         <v>1</v>
@@ -6505,10 +6505,10 @@
         <v>45963</v>
       </c>
       <c r="C243" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.3154761904761905</v>
       </c>
       <c r="D243" t="n">
-        <v>0.130952380952381</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="E243" t="n">
         <v>1</v>
@@ -6530,10 +6530,10 @@
         <v>45970</v>
       </c>
       <c r="C244" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="D244" t="n">
-        <v>0.3035714285714285</v>
+        <v>0.3988095238095238</v>
       </c>
       <c r="E244" t="n">
         <v>1</v>
@@ -6555,10 +6555,10 @@
         <v>45977</v>
       </c>
       <c r="C245" t="n">
-        <v>0.6011904761904762</v>
+        <v>0.3869047619047619</v>
       </c>
       <c r="D245" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="E245" t="n">
         <v>1</v>
@@ -6580,10 +6580,10 @@
         <v>45984</v>
       </c>
       <c r="C246" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="D246" t="n">
-        <v>0.2202380952380952</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="E246" t="n">
         <v>1</v>
@@ -6605,10 +6605,10 @@
         <v>45991</v>
       </c>
       <c r="C247" t="n">
-        <v>0.7678571428571429</v>
+        <v>0.6488095238095238</v>
       </c>
       <c r="D247" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E247" t="n">
         <v>1</v>
@@ -6630,10 +6630,10 @@
         <v>45998</v>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>0.5059523809523809</v>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="E248" t="n">
         <v>1</v>
@@ -6655,10 +6655,10 @@
         <v>46005</v>
       </c>
       <c r="C249" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="D249" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.2678571428571428</v>
       </c>
       <c r="E249" t="n">
         <v>1</v>
@@ -6680,10 +6680,10 @@
         <v>46012</v>
       </c>
       <c r="C250" t="n">
-        <v>0.9940476190476191</v>
+        <v>0.9821428571428571</v>
       </c>
       <c r="D250" t="n">
-        <v>0.005952380952380952</v>
+        <v>0.01785714285714286</v>
       </c>
       <c r="E250" t="n">
         <v>1</v>
@@ -6705,10 +6705,10 @@
         <v>46019</v>
       </c>
       <c r="C251" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="D251" t="n">
-        <v>0.02976190476190476</v>
+        <v>0.05952380952380952</v>
       </c>
       <c r="E251" t="n">
         <v>1</v>
@@ -6730,10 +6730,10 @@
         <v>46026</v>
       </c>
       <c r="C252" t="n">
-        <v>0.6845238095238095</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="D252" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="E252" t="n">
         <v>1</v>
@@ -6755,19 +6755,19 @@
         <v>46033</v>
       </c>
       <c r="C253" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.08148148148148149</v>
       </c>
       <c r="D253" t="n">
-        <v>0.3115942028985507</v>
+        <v>0.1259259259259259</v>
       </c>
       <c r="E253" t="n">
-        <v>0.8214285714285714</v>
+        <v>0.8035714285714286</v>
       </c>
       <c r="F253" t="n">
         <v>168</v>
       </c>
       <c r="G253" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="254">
@@ -6780,10 +6780,10 @@
         <v>46040</v>
       </c>
       <c r="C254" t="n">
-        <v>0.3869047619047619</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="D254" t="n">
-        <v>0.244047619047619</v>
+        <v>0.2976190476190476</v>
       </c>
       <c r="E254" t="n">
         <v>1</v>
@@ -6805,10 +6805,10 @@
         <v>46047</v>
       </c>
       <c r="C255" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.1845238095238095</v>
       </c>
       <c r="D255" t="n">
-        <v>0.2976190476190476</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="E255" t="n">
         <v>1</v>
@@ -6830,10 +6830,10 @@
         <v>46054</v>
       </c>
       <c r="C256" t="n">
-        <v>0.5535714285714286</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="D256" t="n">
-        <v>0.1547619047619048</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="E256" t="n">
         <v>1</v>
@@ -6855,10 +6855,10 @@
         <v>46061</v>
       </c>
       <c r="C257" t="n">
-        <v>0.5178571428571429</v>
+        <v>0.1726190476190476</v>
       </c>
       <c r="D257" t="n">
-        <v>0.3154761904761905</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="E257" t="n">
         <v>1</v>
@@ -6880,10 +6880,10 @@
         <v>46068</v>
       </c>
       <c r="C258" t="n">
-        <v>0.7559523809523809</v>
+        <v>0.4880952380952381</v>
       </c>
       <c r="D258" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="E258" t="n">
         <v>1</v>
@@ -6905,10 +6905,10 @@
         <v>46075</v>
       </c>
       <c r="C259" t="n">
-        <v>0.6547619047619048</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="D259" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="E259" t="n">
         <v>1</v>
@@ -6930,10 +6930,10 @@
         <v>46082</v>
       </c>
       <c r="C260" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.1964285714285714</v>
       </c>
       <c r="D260" t="n">
-        <v>0.119047619047619</v>
+        <v>0.1607142857142857</v>
       </c>
       <c r="E260" t="n">
         <v>1</v>
@@ -6955,10 +6955,10 @@
         <v>46089</v>
       </c>
       <c r="C261" t="n">
-        <v>0.9940476190476191</v>
+        <v>0.7023809523809523</v>
       </c>
       <c r="D261" t="n">
-        <v>0.005952380952380952</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="E261" t="n">
         <v>1</v>
@@ -7030,10 +7030,10 @@
         <v>46110</v>
       </c>
       <c r="C264" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="D264" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1547619047619048</v>
       </c>
       <c r="E264" t="n">
         <v>1</v>
@@ -7055,10 +7055,10 @@
         <v>46117</v>
       </c>
       <c r="C265" t="n">
-        <v>0.6726190476190477</v>
+        <v>0.3035714285714285</v>
       </c>
       <c r="D265" t="n">
-        <v>0.08928571428571429</v>
+        <v>0.2261904761904762</v>
       </c>
       <c r="E265" t="n">
         <v>1</v>
@@ -7080,10 +7080,10 @@
         <v>46124</v>
       </c>
       <c r="C266" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="D266" t="n">
-        <v>0.2261904761904762</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="E266" t="n">
         <v>1</v>
@@ -7105,19 +7105,19 @@
         <v>46131</v>
       </c>
       <c r="C267" t="n">
-        <v>0.65</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="D267" t="n">
-        <v>0.3</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="E267" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="F267" t="n">
         <v>24</v>
       </c>
       <c r="G267" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -7191,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>569</v>
+        <v>3664</v>
       </c>
       <c r="D2" t="n">
-        <v>569</v>
+        <v>3664</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -7207,11 +7207,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>wide_interval</t>
+          <t>supported</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -7230,23 +7230,23 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>732</v>
+        <v>15588</v>
       </c>
       <c r="D3" t="n">
-        <v>732</v>
+        <v>3004</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>variable_regime_public</t>
+          <t>variable_public_fallback</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>adequate</t>
+          <t>limited_regime_support</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -7269,10 +7269,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>1106</v>
+        <v>3520</v>
       </c>
       <c r="D4" t="n">
-        <v>1106</v>
+        <v>3520</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -7308,10 +7308,10 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>524</v>
+        <v>5400</v>
       </c>
       <c r="D5" t="n">
-        <v>524</v>
+        <v>5400</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -7347,23 +7347,23 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>465</v>
+        <v>2748</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>2748</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -7386,10 +7386,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>465</v>
+        <v>11691</v>
       </c>
       <c r="D7" t="n">
-        <v>97</v>
+        <v>2253</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -7425,10 +7425,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>247</v>
+        <v>2640</v>
       </c>
       <c r="D8" t="n">
-        <v>247</v>
+        <v>2640</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -7464,23 +7464,23 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>465</v>
+        <v>4050</v>
       </c>
       <c r="D9" t="n">
-        <v>98</v>
+        <v>4050</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>variable_public_fallback</t>
+          <t>variable_regime_public</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>limited_regime_support</t>
+          <t>adequate</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
